--- a/lab/ornek/fx-blotter-sample.xlsx
+++ b/lab/ornek/fx-blotter-sample.xlsx
@@ -91,7 +91,7 @@
     <row r="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">SAMPLE BANK TREASURY - FX DEAL BLOTTER (SYNTHETIC SAMPLE, NOT REAL DATA)</t>
+          <t xml:space="preserve">SAMPLE BANK TREASURY - FX DEAL BLOTTER (EXAMPLE)</t>
         </is>
       </c>
     </row>
